--- a/medford_uretroskopy.xlsx
+++ b/medford_uretroskopy.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Уретроскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax — всего 5 позиций.</t>
+          <t>Уретроскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_uretroskopy.xlsx
+++ b/medford_uretroskopy.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать уретроскопы для клиники?</t>
+          <t>Что такое уретроскоп?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Глубина резкости, мм, Угол поля зрения, °, Диаметр дистального конца, мм, Диаметр вводимой трубки, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Уретроскоп — эндоскопический прибор для детального осмотра внутренней поверхности мочеиспускательного канала и прилежащих отделов мочевыводящих путей. Он позволяет выявить воспаления, стриктуры, опухоли и инородные тела, а через инструментальный канал — проводить малоинвазивные лечебные манипуляции под визуальным контролем.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Что такое уретерореноскоп?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Уретерореноскоп — разновидность гибкого эндоскопа для осмотра мочеточника и чашечно-лоханочной системы почки при ретроградном доступе. Модели вроде Olympus URF-P7 и Pentax FUR-9RBS имеют тонкий дистальный конец и рабочую длину около 670–700 мм, чтобы дойти до верхних мочевыводящих путей и работать корзинкой или лазером.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем отличается цистоскопия от уретроскопии?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Olympus, Pentax. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Уретроскопия — осмотр мочеиспускательного канала (уретры). Цистоскопия — осмотр полости мочевого пузыря. Часто их выполняют последовательно одним визитом, оценивая уретру при введении прибора, а затем мочевой пузырь. Комбинированные и полужёсткие приборы позволяют проводить обе процедуры.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какой уретроскоп выбрать — жёсткий, полужёсткий или гибкий?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Жёсткий подходит для диагностики у женщин с коротким прямым каналом. Полужёсткий с небольшим прогибом применяют у пациентов обоих полов. Гибкий с фиброволоконной оптикой отклоняется на большие углы, проходит извитые пути и нужен для уретерореноскопии. Тип подбирают под цель процедуры и анатомию.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Болезненна ли уретроскопия?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Процедуру обычно проводят амбулаторно под местной анестезией: у мужчин применяют лидокаиновый гель в уретру, у женщин — спрей. При сложных манипуляциях возможен кратковременный внутривенный наркоз. Тонкий гибкий прибор снижает дискомфорт. Конкретную тактику обезболивания определяет врач.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Как проводится уретроскопия?</t>
+          <t>Можно ли использовать уретроскоп с любой видеостойкой?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Только при совместимости коннектора и протокола. Многие современные модели рассчитаны на вывод изображения на монитор, но эндоскоп, камера и источник света должны образовывать одну платформу. Перед покупкой сверьте совместимость с имеющейся стойкой и набором расходников.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Чем отличается цистоскопия от уретроскопии?</t>
+          <t>Как обрабатывают гибкий уретероскоп?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Гибкий уретероскоп нельзя автоклавировать — высокая температура повреждает фиброволоконную оптику. Между пациентами прибор очищают и подвергают химической стерилизации или дезинфекции высокого уровня по инструкции производителя. Аккуратная обработка каналов продлевает срок службы дорогостоящего инструмента.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Уретроскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax.</t>
+          <t>Уретроскопы — эндоскопические приборы для осмотра слизистой мочеиспускательного канала и прилежащих отделов мочевыводящих путей. В категории представлены гибкие уретерореноскопы и фиброуретероскопы Olympus (URF-P7, URF-P6, URF-P5), уретероренофиброскоп Pentax FUR-9RBS и гибкий уретероскоп PUSEN PU3022A. Диаметр дистального конца моделей — от 1,63 мм (Olympus URF-P6) до 3,0 мм (Pentax FUR-9RBS), диаметр вводимой трубки — 2,65–3,1 мм, рабочая длина — 670–700 мм. Гибкая рабочая часть отклоняется на большие углы и проходит по извитым мочевыводящим путям под визуальным контролем.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы уретроскопов по конструкции</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое уретроскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3347,215 +3347,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы уретроскопов по конструкции</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Жёсткий</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Глубина резкости, мм</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Угол поля зрения, °</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр дистального конца, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр вводимой трубки, мм</t>
+          <t>Гибкий</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Гибкий уретерореноскоп Olympus URF-P7</t>
+          <t>Рабочая часть</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>Прямая, без изгиба</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2-50</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2,65</t>
+          <t>Отклоняется на большие углы</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Гибкий супертонкий уретероскоп Olympus URF-P6</t>
+          <t>Оптика</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>Стержне-линзовая</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2-50</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2,65</t>
+          <t>Фиброволоконная</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Уретероренофиброскоп Pentax FUR-9RBS</t>
+          <t>Основное применение</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>Диагностика при короткой прямой уретре</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1-50</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Норма 90°/ в воде 64°</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>3,1</t>
+          <t>Уретерореноскопия, сложная анатомия</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Фиброуретероскоп Olympus URF-P5</t>
+          <t>Травматизм</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>Выше при извитых путях</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2,5-50</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>2,8</t>
+          <t>Минимальный</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Гибкий уретероскоп PUSEN PU3022A</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>Пример из каталога</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>3-50</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Olympus URF-P7, Pentax FUR-9RBS</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3567,7 +3478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3893,12 +3804,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип процедуры</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается уретроскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Диагностическая уретроскопия у женщин с коротким прямым каналом допускает жёсткий прибор, а ретроградная уретерореноскопия с заходом в мочеточник и почку требует гибкого уретероскопа. От задачи зависит выбор конструкции и диаметра.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3938,12 +3849,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите конструкцию</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Жёсткие — металлическая трубка со стержне-линзовой оптикой без изгиба. Полужёсткие допускают небольшой прогиб. Гибкие оснащены фиброволоконной оптикой, отклоняются на большие углы и минимизируют травматизм при сложной анатомии. В каталоге — гибкие модели Olympus, Pentax, PUSEN.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3983,12 +3894,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сверьте диаметр дистального конца</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Глубина резкости, мм, Угол поля зрения, °, Диаметр дистального конца, мм, Диаметр вводимой трубки, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Чем тоньше кончик, тем легче проход по мочеточнику. В каталоге дистальный конец от 1,63 мм (Olympus URF-P6) до 3,0 мм (Pentax FUR-9RBS), диаметр вводимой трубки 2,65–3,1 мм. Тонкий прибор снижает болезненность и риск травмы слизистой.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4028,12 +3939,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте рабочую длину и угол обзора</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Olympus, Pentax.</t>
+          <t>Рабочая длина 670–700 мм рассчитана на доступ к верхним мочевыводящим путям. Угол поля зрения у моделей около 90–120°; у Pentax FUR-9RBS в воде он меняется на 64°. Сопоставьте параметры с планируемым уровнем вмешательства.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4073,12 +3984,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Уточните инструментальный канал</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Через рабочий канал подают лазерное волокно, корзинки для конкрементов и щипцы для биопсии, а также стерильный раствор для расправления стенок. Убедитесь, что диаметр канала совместим с используемыми расходниками и лазерной системой клиники.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4118,12 +4029,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Заложите обработку и совместимость с видео</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Гибкий уретероскоп проходит химическую дезинфекцию и не терпит высоких температур автоклава. Многие модели совместимы с видеоаппаратурой для вывода изображения на монитор и документирования. Проверьте коннектор к вашей стойке и парк расходников.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4173,7 +4084,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Уретроскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Olympus, Pentax. При выборе обращают внимание на глубина резкости, угол поля зрения, диаметр дистального конца, диаметр вводимой трубки, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Для ретроградной уретерореноскопии выбирайте гибкий прибор с минимальным диаметром дистального конца — 1,63–1,8 мм у супертонких Olympus URF-P6 и URF-P5 облегчают проход по мочеточнику. Смотрите на угол отклонения рабочей части и наличие инструментального канала для лазерного волокна и корзинок. Рабочая длина 670–700 мм рассчитана на доступ до чашечно-лоханочной системы. Тип уретроскопа под задачу подбирает клиника вместе с оперирующим урологом.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4457,13 +4368,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое уретроскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Уретроскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Olympus, Pentax. Подберём вариант под задачи вашего отделения.</t>
+          <t>Уретроскоп — эндоскоп для визуального осмотра уретры и мочевыводящих путей и малоинвазивных манипуляций под контролем зрения. По конструкции различают жёсткие, полужёсткие и гибкие приборы; гибкие оснащены фиброволоконной оптикой, отклоняются на большие углы и подходят при сложной анатомии и для уретерореноскопии верхних мочевыводящих путей. В каталоге — гибкие уретерореноскопы и фиброуретероскопы Olympus URF-P7, URF-P6, URF-P5, уретероренофиброскоп Pentax FUR-9RBS и PUSEN PU3022A с диаметром дистального конца 1,63–3,0 мм, диаметром трубки 2,65–3,1 мм и рабочей длиной 670–700 мм.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4500,13 +4411,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое уретроскоп и зачем он нужен</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Глубина резкости, мм, Угол поля зрения, °, Диаметр дистального конца, мм, Диаметр вводимой трубки, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Уретроскоп — медицинский эндоскоп для визуального осмотра уретры и мочевыводящих путей. Он выявляет воспаления, стриктуры, опухоли и инородные тела, а через инструментальный канал позволяет брать биопсию, дробить и извлекать конкременты. Гибкие уретерореноскопы дополнительно дают доступ к мочеточнику и почке при ретроградных операциях.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4543,13 +4454,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Как устроен уретроскоп</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>В основе прибора — оптическая система с источником холодного света и световодом, рукоятка с питанием и управлением, а у жёстких моделей — сменные тубусы разного диаметра по шкале Шарьера с обтюратором для защиты слизистой. Внутри проходит инструментальный канал для подачи инструментов и раствора. Гибкие модели используют фиброволоконную оптику.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4586,13 +4497,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды уретроскопов по конструкции</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Жёсткие — прямая металлическая трубка со стержне-линзовой оптикой, применяются в диагностике при короткой прямой уретре. Полужёсткие допускают небольшой прогиб и подходят пациентам обоих полов. Гибкие с фиброволоконной оптикой отклоняются на большие углы, минимизируют травматизм и нужны для уретерореноскопии верхних мочевыводящих путей.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4609,6 +4520,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как подобрать модель под клинику</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Отталкивайтесь от вида вмешательства: для ретроградной уретерореноскопии важны тонкий дистальный конец (1,63–1,8 мм), рабочая длина 670–700 мм и совместимость канала с лазером и корзинками. Сверяйте угол обзора и коннектор к видеостойке. В каталоге — гибкие модели Olympus URF-P7, URF-P6, URF-P5, Pentax FUR-9RBS и PUSEN PU3022A.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>uretroskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
